--- a/agliluz/dashboard_inteligencia_mercado.xlsx
+++ b/agliluz/dashboard_inteligencia_mercado.xlsx
@@ -520,20 +520,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057472-84-LP26</t>
+          <t>1057472-9-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
+          <t>CONVENIO DE MANTENIMIENTO TOMÓGRAFO COMPUTARIZADO</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-18T16:00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,20 +601,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1150-14-O126</t>
+          <t>1263503-3-O126</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA III</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T11:05:52.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -682,20 +682,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211839-53-LE26</t>
+          <t>1057472-84-LP26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -711,12 +711,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -763,20 +763,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057472-85-LP26</t>
+          <t>1150-14-O126</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
+          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -844,20 +844,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1225288-5-LE26</t>
+          <t>1211839-53-LE26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
+          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-26T16:30:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -925,20 +925,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1233616-49-LE26</t>
+          <t>2186-21-LE26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
+          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-18T12:00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1006,12 +1006,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1233616-51-L126</t>
+          <t>1263503-2-O126</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-03T15:04:02.473</t>
+          <t>2026-08-03T11:03:43.517</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1330,20 +1330,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1798-5-LE26</t>
+          <t>1048-55-LE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
+          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-24T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1411,12 +1411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1951-31-LE26</t>
+          <t>1063538-165-LP26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
+          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-03T15:31:00</t>
+          <t>2026-08-03T16:15:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1492,20 +1492,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2322-53-LR26</t>
+          <t>1063538-185-LP26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
+          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-14T15:15:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1573,12 +1573,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2328-44-LE26</t>
+          <t>1344402-6-E226</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
+          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-03T15:03:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2342-30-LP26</t>
+          <t>2332-78-L126</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
+          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2744-26-L126</t>
+          <t>2345-127-LE26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-10T15:47:00</t>
+          <t>2026-08-17T15:01:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1816,20 +1816,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3326-35-LE26</t>
+          <t>2765-44-E226</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
+          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-03T18:03:05.86</t>
+          <t>2026-08-10T16:23:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1897,20 +1897,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3399-17-L126</t>
+          <t>3390-21-LE26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
+          <t>Materiales para Mantenimiento y Reparaciones.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-30T15:56:00</t>
+          <t>2026-08-03T15:57:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1978,20 +1978,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3296-19-LE25</t>
+          <t>3562-28-LR26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
+          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-08T19:55:00</t>
+          <t>2026-09-03T16:37:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2059,20 +2059,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1186-2-LE26</t>
+          <t>1389488-17-LP26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
+          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-06-04T16:37:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2140,20 +2140,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1225288-2-LE26</t>
+          <t>1658-151-LP26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
+          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-26T16:30:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2221,20 +2221,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1263503-1-O126</t>
+          <t>2403-52-LP26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
+          <t>Reposición calzada pasaje Maracaibo</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-03T10:51:48.64</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2302,12 +2302,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1306643-23-LE26</t>
+          <t>2744-26-L126</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-18T15:00:00</t>
+          <t>2026-08-10T15:47:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2383,20 +2383,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1048-55-LE26</t>
+          <t>3326-35-LE26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
+          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T18:03:05.86</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2464,12 +2464,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1063538-165-LP26</t>
+          <t>2328-43-LE26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
+          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-03T16:15:00</t>
+          <t>2026-08-03T15:52:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2545,12 +2545,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1063538-185-LP26</t>
+          <t>1186-2-LE26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
+          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-14T15:15:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2626,20 +2626,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1344402-6-E226</t>
+          <t>1225288-2-LE26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
+          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-06-26T16:30:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2707,20 +2707,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057472-9-LP26</t>
+          <t>1263503-1-O126</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO TOMÓGRAFO COMPUTARIZADO</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-18T16:00:00</t>
+          <t>2026-08-03T10:51:48.64</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2788,20 +2788,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1263503-3-O126</t>
+          <t>1306643-23-LE26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA III</t>
+          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-03T11:05:52.27</t>
+          <t>2026-08-18T15:00:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2869,20 +2869,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3482-6-LE26</t>
+          <t>2788-33-LP26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mantenimiento y Reparación de Baño.</t>
+          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-10T16:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2950,20 +2950,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4483-15-LR26</t>
+          <t>3565-54-LE26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
+          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-30T15:30:00</t>
+          <t>2026-08-14T12:24:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3031,12 +3031,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4494-47-LE26</t>
+          <t>4412-20-LP26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
+          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-18T15:00:00</t>
+          <t>2026-09-02T15:30:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3112,20 +3112,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>584264-35-LR26</t>
+          <t>5908-25-LP26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
+          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-04T15:05:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3193,20 +3193,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>608897-45-LE26</t>
+          <t>3399-17-L126</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
+          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-13T16:00:00</t>
+          <t>2026-07-30T15:56:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3274,12 +3274,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>610-13-LP26</t>
+          <t>3482-6-LE26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
+          <t>Mantenimiento y Reparación de Baño.</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-21T15:00:00</t>
+          <t>2026-08-10T16:00:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3355,20 +3355,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2274-30-LE26</t>
+          <t>1057472-85-LP26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
+          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-03T18:40:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3436,20 +3436,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2328-46-LE26</t>
+          <t>1225288-5-LE26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
+          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-06-26T16:30:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3517,20 +3517,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1263503-2-O126</t>
+          <t>1233616-49-LE26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
+          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-03T11:03:43.517</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3598,20 +3598,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2328-43-LE26</t>
+          <t>1233616-51-L126</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
+          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-03T15:52:00</t>
+          <t>2026-08-03T15:04:02.473</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3679,20 +3679,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057472-87-LP26</t>
+          <t>1085111-21-LR26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
+          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3760,20 +3760,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1133353-35-LP26</t>
+          <t>1133353-34-LE26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
+          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-13T17:30:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1198-24-LE26</t>
+          <t>1232565-25-L126</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mantención y Obras Menores Estadio San Felipe</t>
+          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-08-10T17:00:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3922,20 +3922,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1199-11-LE26</t>
+          <t>1263503-4-O126</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-03T17:00:00</t>
+          <t>2026-08-03T11:07:24.06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4003,20 +4003,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1369-14-O126</t>
+          <t>3080-2-L126</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
+          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-07T18:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4084,20 +4084,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1481-5-L126</t>
+          <t>3436-86-L126</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
+          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-22T15:00:00</t>
+          <t>2026-08-03T15:10:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4165,20 +4165,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2467-79-LE26</t>
+          <t>3562-31-LR26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
+          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-03T15:20:00</t>
+          <t>2026-09-03T16:00:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4246,12 +4246,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2760-100-LE26</t>
+          <t>359-91-LE26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
+          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4320,27 +4320,27 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Plataforma Interact</t>
+          <t>Sin requerimientos de control específicos</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2793-104-LE26</t>
+          <t>3938-25-LE26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
+          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-21T16:20:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4408,20 +4408,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2981-204-LE26</t>
+          <t>3968-35-LE26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
+          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-14T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4489,20 +4489,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3084-15-R126</t>
+          <t>4118-5-LP26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
+          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-03T15:00:00</t>
+          <t>2026-08-25T12:00:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4570,20 +4570,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3621-39-LE26</t>
+          <t>618472-3-L126</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
+          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-03T16:20:00</t>
+          <t>2026-08-12T08:00:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4651,12 +4651,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3693-141-CO26</t>
+          <t>707426-25-LP26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
+          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4732,20 +4732,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>407-86-LE26</t>
+          <t>740-12-LE26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
+          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-03T10:53:14.54</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4813,20 +4813,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2186-21-LE26</t>
+          <t>761391-107-L126</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
+          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-18T12:00:00</t>
+          <t>2026-07-21T15:00:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4894,20 +4894,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2332-78-L126</t>
+          <t>802-11-LE26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
+          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4975,20 +4975,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3296-1-LE26</t>
+          <t>826-11-O126</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
+          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-16T09:00:00</t>
+          <t>2026-08-19T09:00:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5056,20 +5056,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2345-127-LE26</t>
+          <t>2274-30-LE26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
+          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-17T15:01:00</t>
+          <t>2026-08-03T18:40:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5137,20 +5137,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2765-44-E226</t>
+          <t>2328-46-LE26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
+          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-10T16:23:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5218,20 +5218,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3390-21-LE26</t>
+          <t>4261-4-LE26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Materiales para Mantenimiento y Reparaciones.</t>
+          <t>MTS Conservación CDI España Comuna de Angol</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-03T15:57:00</t>
+          <t>2026-08-03T16:20:14.27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5299,20 +5299,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3562-28-LR26</t>
+          <t>545598-24-LE26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
+          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-03T16:37:00</t>
+          <t>2026-07-17T15:04:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5380,12 +5380,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>633-43-L126</t>
+          <t>584105-14-LP26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
+          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-10T19:00:00</t>
+          <t>2026-08-24T15:01:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5461,20 +5461,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>750998-47-LP26</t>
+          <t>673663-15-LP26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
+          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-03T15:15:00</t>
+          <t>2026-08-03T13:18:45.21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5542,20 +5542,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>934-11-LE26</t>
+          <t>697057-29-LE26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
+          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-09-03T11:00:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5623,12 +5623,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>935-17-LE26</t>
+          <t>1434-21-LE26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
+          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-14T09:00:00</t>
+          <t>2026-08-17T15:01:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5704,20 +5704,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>967490-14-LE26</t>
+          <t>1506668-9-LE26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
+          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-21T15:30:00</t>
+          <t>2026-08-03T17:30:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5785,20 +5785,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1389488-17-LP26</t>
+          <t>2157-78-LP26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
+          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-04T16:37:00</t>
+          <t>2026-08-03T17:19:08.62</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5866,20 +5866,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1658-151-LP26</t>
+          <t>2183-9-LP26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
+          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-03T15:47:10.15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5947,20 +5947,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2403-52-LP26</t>
+          <t>2261-21-O126</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Reposición calzada pasaje Maracaibo</t>
+          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-09-03T09:00:00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6028,12 +6028,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4412-20-LP26</t>
+          <t>812799-44-LP26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
+          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-02T15:30:00</t>
+          <t>2026-08-31T15:00:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6109,20 +6109,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5908-25-LP26</t>
+          <t>821-8-O126</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
+          <t>Reposición Cuartel BICRIM Ovalle</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-03T08:26:23.16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6190,20 +6190,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>812799-44-LP26</t>
+          <t>932-21-LE26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
+          <t>Mantenimiento preventivo y correctivo presurizador</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-31T15:00:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6271,20 +6271,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>821-8-O126</t>
+          <t>3296-1-LE26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Reposición Cuartel BICRIM Ovalle</t>
+          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-03T08:26:23.16</t>
+          <t>2026-01-16T09:00:00</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6352,20 +6352,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>932-21-LE26</t>
+          <t>1057472-87-LP26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mantenimiento preventivo y correctivo presurizador</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6433,20 +6433,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3080-2-L126</t>
+          <t>1133353-35-LP26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
+          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-13T17:30:00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6514,20 +6514,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3436-86-L126</t>
+          <t>1198-24-LE26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
+          <t>Mantención y Obras Menores Estadio San Felipe</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-03T15:10:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6595,20 +6595,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3562-31-LR26</t>
+          <t>1199-11-LE26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
+          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-03T16:00:00</t>
+          <t>2026-08-03T17:00:00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6676,20 +6676,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>359-91-LE26</t>
+          <t>1369-14-O126</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
+          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-09-07T18:00:00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6757,12 +6757,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3938-25-LE26</t>
+          <t>2430-61-LR26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
+          <t>“REPOSICIÓN Y MANTENCIÓN SISTEMA DE AUDIO DEL ESTADIO REGIONAL CALVO Y BASCUÑAN ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-21T16:20:00</t>
+          <t>2026-09-17T11:00:00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6838,20 +6838,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3968-35-LE26</t>
+          <t>2704-57-LP26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
+          <t>SC 3935 Servicio Mantenimiento prev y Correctivo de Calderas estufas de Tiro Balanceado termos</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-13T20:00:00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6919,12 +6919,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4118-5-LP26</t>
+          <t>2792-9-L126</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
+          <t>REPOSICIÓN DE SILLÓN DENTAL PARA CESFAM LA PINCOYA</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-25T12:00:00</t>
+          <t>2026-08-13T09:00:00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7000,20 +7000,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2788-33-LP26</t>
+          <t>3416-45-L126</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
+          <t xml:space="preserve">SERV. DE MANTENIMIENTO Y REPARACIÓN DE EQUIPOS </t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-10T15:30:00</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7081,20 +7081,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3565-54-LE26</t>
+          <t>3693-145-LE26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
+          <t>ADQUISICIÓN DE VESTUARIO DEPORTIVO PARA ESTUDIANTE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-14T12:24:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7162,20 +7162,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>638-15-LE26</t>
+          <t>633-43-L126</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>REPARACIÓN MANTENIMIENTO Y NORMALIZACIÓN QUINCHO</t>
+          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-20T15:30:00</t>
+          <t>2026-08-10T19:00:00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7243,20 +7243,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>898-42-R126</t>
+          <t>750998-47-LP26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO CENTRALES DE GASES CLINICOS</t>
+          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-23T15:00:00</t>
+          <t>2026-08-03T15:15:00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7324,20 +7324,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4261-4-LE26</t>
+          <t>934-11-LE26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MTS Conservación CDI España Comuna de Angol</t>
+          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-03T16:20:14.27</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7405,20 +7405,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>545598-24-LE26</t>
+          <t>935-17-LE26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
+          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-17T15:04:00</t>
+          <t>2026-08-14T09:00:00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7486,12 +7486,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>584105-14-LP26</t>
+          <t>967490-14-LE26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
+          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-24T15:01:00</t>
+          <t>2026-08-21T15:30:00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -7567,20 +7567,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>673663-15-LP26</t>
+          <t>3882-71-LE26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
+          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-03T13:18:45.21</t>
+          <t>2026-08-17T15:00:00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7648,20 +7648,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>697057-29-LE26</t>
+          <t>407-101-LP26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
+          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-03T11:00:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7729,20 +7729,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>618472-3-L126</t>
+          <t>4366-22-LP26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
+          <t>Rotura y reposición pavimento asfáltico</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-12T08:00:00</t>
+          <t>2026-08-03T15:04:02.44</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7810,12 +7810,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>707426-25-LP26</t>
+          <t>4487-29-LE26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
+          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7891,20 +7891,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>740-12-LE26</t>
+          <t>5194-3-LE26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
+          <t>Adquisicion de Equipos Deportivos</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-31T16:30:00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7972,20 +7972,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>761391-107-L126</t>
+          <t>980313-25-LP26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
+          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-21T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -8053,12 +8053,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>802-11-LE26</t>
+          <t>1798-5-LE26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
+          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-07-24T15:00:00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8134,20 +8134,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>826-11-O126</t>
+          <t>1951-31-LE26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
+          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-19T09:00:00</t>
+          <t>2026-08-03T15:31:00</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8215,12 +8215,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1085111-21-LR26</t>
+          <t>2322-53-LR26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
+          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8296,12 +8296,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1133353-34-LE26</t>
+          <t>2328-44-LE26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
+          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T15:03:00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8377,20 +8377,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1232565-25-L126</t>
+          <t>2342-30-LP26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
+          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-10T17:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8458,20 +8458,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1263503-4-O126</t>
+          <t>3296-19-LE25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
+          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-03T11:07:24.06</t>
+          <t>2026-01-08T19:55:00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -8539,20 +8539,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1434-21-LE26</t>
+          <t>4483-15-LR26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
+          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-17T15:01:00</t>
+          <t>2026-06-30T15:30:00</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8620,20 +8620,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1506668-9-LE26</t>
+          <t>4494-47-LE26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
+          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-03T17:30:00</t>
+          <t>2026-08-18T15:00:00</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8701,20 +8701,20 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2157-78-LP26</t>
+          <t>584264-35-LR26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
+          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-03T17:19:08.62</t>
+          <t>2026-09-04T15:05:00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8782,20 +8782,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2183-9-LP26</t>
+          <t>608897-45-LE26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
+          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-03T15:47:10.15</t>
+          <t>2026-08-13T16:00:00</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8863,12 +8863,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2261-21-O126</t>
+          <t>610-13-LP26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
+          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-03T09:00:00</t>
+          <t>2026-08-21T15:00:00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8944,20 +8944,20 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2430-61-LR26</t>
+          <t>1481-5-L126</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>“REPOSICIÓN Y MANTENCIÓN SISTEMA DE AUDIO DEL ESTADIO REGIONAL CALVO Y BASCUÑAN ANTOFAGASTA”</t>
+          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-17T11:00:00</t>
+          <t>2026-07-22T15:00:00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9025,20 +9025,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2704-57-LP26</t>
+          <t>2467-79-LE26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SC 3935 Servicio Mantenimiento prev y Correctivo de Calderas estufas de Tiro Balanceado termos</t>
+          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-13T20:00:00</t>
+          <t>2026-08-03T15:20:00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9106,20 +9106,20 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2792-9-L126</t>
+          <t>2760-100-LE26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>REPOSICIÓN DE SILLÓN DENTAL PARA CESFAM LA PINCOYA</t>
+          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-13T09:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9180,27 +9180,27 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Plataforma Interact</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3416-45-L126</t>
+          <t>2793-104-LE26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. DE MANTENIMIENTO Y REPARACIÓN DE EQUIPOS </t>
+          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-10T15:30:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9268,20 +9268,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3693-145-LE26</t>
+          <t>2981-204-LE26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE VESTUARIO DEPORTIVO PARA ESTUDIANTE</t>
+          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-14T15:00:00</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9297,12 +9297,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9349,20 +9349,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3882-71-LE26</t>
+          <t>3084-15-R126</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
+          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-17T15:00:00</t>
+          <t>2026-06-03T15:00:00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9430,12 +9430,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>407-101-LP26</t>
+          <t>3621-39-LE26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
+          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-03T16:20:00</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9511,20 +9511,20 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4366-22-LP26</t>
+          <t>3693-141-CO26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rotura y reposición pavimento asfáltico</t>
+          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-03T15:04:02.44</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9592,20 +9592,20 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4487-29-LE26</t>
+          <t>407-86-LE26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
+          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-03T10:53:14.54</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9673,20 +9673,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5194-3-LE26</t>
+          <t>638-15-LE26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adquisicion de Equipos Deportivos</t>
+          <t>REPARACIÓN MANTENIMIENTO Y NORMALIZACIÓN QUINCHO</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-31T16:30:00</t>
+          <t>2026-07-20T15:30:00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9754,20 +9754,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>980313-25-LP26</t>
+          <t>898-42-R126</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
+          <t>MANTENIMIENTO PREVENTIVO CENTRALES DE GASES CLINICOS</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-03-23T15:00:00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9881,12 +9881,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057472-84-LP26</t>
+          <t>1057472-9-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
+          <t>CONVENIO DE MANTENIMIENTO TOMÓGRAFO COMPUTARIZADO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9911,12 +9911,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1150-14-O126</t>
+          <t>1263503-3-O126</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA III</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9941,12 +9941,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211839-53-LE26</t>
+          <t>1057472-84-LP26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9964,19 +9964,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057472-85-LP26</t>
+          <t>1150-14-O126</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
+          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10001,12 +10001,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1225288-5-LE26</t>
+          <t>1211839-53-LE26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
+          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -10031,12 +10031,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1233616-49-LE26</t>
+          <t>2186-21-LE26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
+          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -10061,12 +10061,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1233616-51-L126</t>
+          <t>1263503-2-O126</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10181,12 +10181,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1798-5-LE26</t>
+          <t>1048-55-LE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
+          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10211,12 +10211,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1951-31-LE26</t>
+          <t>1063538-165-LP26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
+          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10241,12 +10241,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2322-53-LR26</t>
+          <t>1063538-185-LP26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
+          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10264,19 +10264,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2328-44-LE26</t>
+          <t>1344402-6-E226</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
+          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10294,19 +10294,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2342-30-LP26</t>
+          <t>2332-78-L126</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
+          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10324,19 +10324,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2744-26-L126</t>
+          <t>2345-127-LE26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10354,19 +10354,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3326-35-LE26</t>
+          <t>2765-44-E226</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
+          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10384,19 +10384,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3399-17-L126</t>
+          <t>3390-21-LE26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
+          <t>Materiales para Mantenimiento y Reparaciones.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10421,12 +10421,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3296-19-LE25</t>
+          <t>3562-28-LR26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
+          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -10444,19 +10444,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1186-2-LE26</t>
+          <t>1389488-17-LP26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
+          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -10474,19 +10474,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1225288-2-LE26</t>
+          <t>1658-151-LP26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
+          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10511,12 +10511,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1263503-1-O126</t>
+          <t>2403-52-LP26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
+          <t>Reposición calzada pasaje Maracaibo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -10541,12 +10541,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1306643-23-LE26</t>
+          <t>2744-26-L126</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -10571,12 +10571,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1048-55-LE26</t>
+          <t>3326-35-LE26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
+          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -10594,19 +10594,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1063538-165-LP26</t>
+          <t>2328-43-LE26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
+          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -10624,19 +10624,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1063538-185-LP26</t>
+          <t>1186-2-LE26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
+          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10661,12 +10661,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1344402-6-E226</t>
+          <t>1225288-2-LE26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
+          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -10684,19 +10684,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057472-9-LP26</t>
+          <t>1263503-1-O126</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO TOMÓGRAFO COMPUTARIZADO</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -10721,12 +10721,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1263503-3-O126</t>
+          <t>1306643-23-LE26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA III</t>
+          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -10751,12 +10751,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3482-6-LE26</t>
+          <t>2788-33-LP26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mantenimiento y Reparación de Baño.</t>
+          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -10774,19 +10774,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4483-15-LR26</t>
+          <t>3565-54-LE26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
+          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -10811,12 +10811,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4494-47-LE26</t>
+          <t>4412-20-LP26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
+          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10834,19 +10834,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>584264-35-LR26</t>
+          <t>5908-25-LP26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
+          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10864,19 +10864,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>608897-45-LE26</t>
+          <t>3399-17-L126</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
+          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10901,12 +10901,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>610-13-LP26</t>
+          <t>3482-6-LE26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
+          <t>Mantenimiento y Reparación de Baño.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10931,12 +10931,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2274-30-LE26</t>
+          <t>1057472-85-LP26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
+          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10954,19 +10954,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2328-46-LE26</t>
+          <t>1225288-5-LE26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
+          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10991,12 +10991,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1263503-2-O126</t>
+          <t>1233616-49-LE26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
+          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11021,12 +11021,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2328-43-LE26</t>
+          <t>1233616-51-L126</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
+          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11044,19 +11044,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057472-87-LP26</t>
+          <t>1085111-21-LR26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
+          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11081,12 +11081,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1133353-35-LP26</t>
+          <t>1133353-34-LE26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
+          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11104,19 +11104,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1198-24-LE26</t>
+          <t>1232565-25-L126</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mantención y Obras Menores Estadio San Felipe</t>
+          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11141,12 +11141,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1199-11-LE26</t>
+          <t>1263503-4-O126</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -11164,19 +11164,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1369-14-O126</t>
+          <t>3080-2-L126</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
+          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -11201,12 +11201,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1481-5-L126</t>
+          <t>3436-86-L126</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
+          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -11224,19 +11224,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2467-79-LE26</t>
+          <t>3562-31-LR26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
+          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -11254,19 +11254,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2760-100-LE26</t>
+          <t>359-91-LE26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
+          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Plataforma Interact</t>
+          <t>Sin requerimientos de control específicos</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -11291,12 +11291,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2793-104-LE26</t>
+          <t>3938-25-LE26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
+          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -11314,19 +11314,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2981-204-LE26</t>
+          <t>3968-35-LE26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
+          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -11344,19 +11344,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3084-15-R126</t>
+          <t>4118-5-LP26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
+          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -11374,19 +11374,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3621-39-LE26</t>
+          <t>618472-3-L126</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
+          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -11411,12 +11411,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3693-141-CO26</t>
+          <t>707426-25-LP26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
+          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -11441,12 +11441,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>407-86-LE26</t>
+          <t>740-12-LE26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
+          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -11464,19 +11464,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2186-21-LE26</t>
+          <t>761391-107-L126</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
+          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -11501,12 +11501,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2332-78-L126</t>
+          <t>802-11-LE26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
+          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11524,19 +11524,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3296-1-LE26</t>
+          <t>826-11-O126</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
+          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11561,12 +11561,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2345-127-LE26</t>
+          <t>2274-30-LE26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
+          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -11591,12 +11591,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2765-44-E226</t>
+          <t>2328-46-LE26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
+          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -11614,19 +11614,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3390-21-LE26</t>
+          <t>4261-4-LE26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Materiales para Mantenimiento y Reparaciones.</t>
+          <t>MTS Conservación CDI España Comuna de Angol</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -11651,12 +11651,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3562-28-LR26</t>
+          <t>545598-24-LE26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
+          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -11681,12 +11681,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>633-43-L126</t>
+          <t>584105-14-LP26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
+          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -11711,12 +11711,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>750998-47-LP26</t>
+          <t>673663-15-LP26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
+          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -11734,19 +11734,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>934-11-LE26</t>
+          <t>697057-29-LE26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
+          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -11764,19 +11764,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>935-17-LE26</t>
+          <t>1434-21-LE26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
+          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -11794,19 +11794,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>967490-14-LE26</t>
+          <t>1506668-9-LE26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
+          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -11831,12 +11831,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1389488-17-LP26</t>
+          <t>2157-78-LP26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
+          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -11854,19 +11854,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1658-151-LP26</t>
+          <t>2183-9-LP26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
+          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11884,19 +11884,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2403-52-LP26</t>
+          <t>2261-21-O126</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Reposición calzada pasaje Maracaibo</t>
+          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -11921,12 +11921,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4412-20-LP26</t>
+          <t>812799-44-LP26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
+          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -11944,19 +11944,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5908-25-LP26</t>
+          <t>821-8-O126</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
+          <t>Reposición Cuartel BICRIM Ovalle</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11981,12 +11981,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>812799-44-LP26</t>
+          <t>932-21-LE26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
+          <t>Mantenimiento preventivo y correctivo presurizador</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -12011,12 +12011,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>821-8-O126</t>
+          <t>3296-1-LE26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Reposición Cuartel BICRIM Ovalle</t>
+          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -12041,12 +12041,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>932-21-LE26</t>
+          <t>1057472-87-LP26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mantenimiento preventivo y correctivo presurizador</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -12071,12 +12071,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3080-2-L126</t>
+          <t>1133353-35-LP26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
+          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -12101,12 +12101,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3436-86-L126</t>
+          <t>1198-24-LE26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
+          <t>Mantención y Obras Menores Estadio San Felipe</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12124,19 +12124,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3562-31-LR26</t>
+          <t>1199-11-LE26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
+          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -12161,12 +12161,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>359-91-LE26</t>
+          <t>1369-14-O126</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
+          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -12191,12 +12191,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3938-25-LE26</t>
+          <t>2430-61-LR26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
+          <t>“REPOSICIÓN Y MANTENCIÓN SISTEMA DE AUDIO DEL ESTADIO REGIONAL CALVO Y BASCUÑAN ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12221,12 +12221,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3968-35-LE26</t>
+          <t>2704-57-LP26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
+          <t>SC 3935 Servicio Mantenimiento prev y Correctivo de Calderas estufas de Tiro Balanceado termos</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -12244,19 +12244,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4118-5-LP26</t>
+          <t>2792-9-L126</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
+          <t>REPOSICIÓN DE SILLÓN DENTAL PARA CESFAM LA PINCOYA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -12281,12 +12281,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2788-33-LP26</t>
+          <t>3416-45-L126</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
+          <t xml:space="preserve">SERV. DE MANTENIMIENTO Y REPARACIÓN DE EQUIPOS </t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -12304,19 +12304,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3565-54-LE26</t>
+          <t>3693-145-LE26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
+          <t>ADQUISICIÓN DE VESTUARIO DEPORTIVO PARA ESTUDIANTE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -12334,19 +12334,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>638-15-LE26</t>
+          <t>633-43-L126</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>REPARACIÓN MANTENIMIENTO Y NORMALIZACIÓN QUINCHO</t>
+          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -12364,19 +12364,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>898-42-R126</t>
+          <t>750998-47-LP26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO CENTRALES DE GASES CLINICOS</t>
+          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -12394,19 +12394,19 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4261-4-LE26</t>
+          <t>934-11-LE26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MTS Conservación CDI España Comuna de Angol</t>
+          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -12424,19 +12424,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>545598-24-LE26</t>
+          <t>935-17-LE26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
+          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12461,12 +12461,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>584105-14-LP26</t>
+          <t>967490-14-LE26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
+          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12491,12 +12491,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>673663-15-LP26</t>
+          <t>3882-71-LE26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
+          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12521,12 +12521,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>697057-29-LE26</t>
+          <t>407-101-LP26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
+          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12551,12 +12551,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>618472-3-L126</t>
+          <t>4366-22-LP26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
+          <t>Rotura y reposición pavimento asfáltico</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12581,12 +12581,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>707426-25-LP26</t>
+          <t>4487-29-LE26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
+          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12611,12 +12611,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>740-12-LE26</t>
+          <t>5194-3-LE26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
+          <t>Adquisicion de Equipos Deportivos</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12641,12 +12641,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>761391-107-L126</t>
+          <t>980313-25-LP26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
+          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -12664,19 +12664,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>802-11-LE26</t>
+          <t>1798-5-LE26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
+          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -12694,19 +12694,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>826-11-O126</t>
+          <t>1951-31-LE26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
+          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -12731,12 +12731,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1085111-21-LR26</t>
+          <t>2322-53-LR26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
+          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -12754,19 +12754,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1133353-34-LE26</t>
+          <t>2328-44-LE26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
+          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -12791,12 +12791,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1232565-25-L126</t>
+          <t>2342-30-LP26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
+          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -12821,12 +12821,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1263503-4-O126</t>
+          <t>3296-19-LE25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
+          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -12851,12 +12851,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1434-21-LE26</t>
+          <t>4483-15-LR26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
+          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -12881,12 +12881,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1506668-9-LE26</t>
+          <t>4494-47-LE26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
+          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -12904,19 +12904,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2157-78-LP26</t>
+          <t>584264-35-LR26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
+          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -12934,19 +12934,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2183-9-LP26</t>
+          <t>608897-45-LE26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
+          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12971,12 +12971,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2261-21-O126</t>
+          <t>610-13-LP26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
+          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -13001,12 +13001,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2430-61-LR26</t>
+          <t>1481-5-L126</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>“REPOSICIÓN Y MANTENCIÓN SISTEMA DE AUDIO DEL ESTADIO REGIONAL CALVO Y BASCUÑAN ANTOFAGASTA”</t>
+          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -13031,12 +13031,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2704-57-LP26</t>
+          <t>2467-79-LE26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SC 3935 Servicio Mantenimiento prev y Correctivo de Calderas estufas de Tiro Balanceado termos</t>
+          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -13061,12 +13061,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2792-9-L126</t>
+          <t>2760-100-LE26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>REPOSICIÓN DE SILLÓN DENTAL PARA CESFAM LA PINCOYA</t>
+          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Plataforma Interact</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -13091,12 +13091,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3416-45-L126</t>
+          <t>2793-104-LE26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. DE MANTENIMIENTO Y REPARACIÓN DE EQUIPOS </t>
+          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -13121,12 +13121,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3693-145-LE26</t>
+          <t>2981-204-LE26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE VESTUARIO DEPORTIVO PARA ESTUDIANTE</t>
+          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -13144,19 +13144,19 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3882-71-LE26</t>
+          <t>3084-15-R126</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
+          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -13174,19 +13174,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>407-101-LP26</t>
+          <t>3621-39-LE26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
+          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -13211,12 +13211,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4366-22-LP26</t>
+          <t>3693-141-CO26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rotura y reposición pavimento asfáltico</t>
+          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -13241,12 +13241,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4487-29-LE26</t>
+          <t>407-86-LE26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
+          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -13271,12 +13271,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5194-3-LE26</t>
+          <t>638-15-LE26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adquisicion de Equipos Deportivos</t>
+          <t>REPARACIÓN MANTENIMIENTO Y NORMALIZACIÓN QUINCHO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -13294,19 +13294,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>980313-25-LP26</t>
+          <t>898-42-R126</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
+          <t>MANTENIMIENTO PREVENTIVO CENTRALES DE GASES CLINICOS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
     </row>

--- a/agliluz/dashboard_inteligencia_mercado.xlsx
+++ b/agliluz/dashboard_inteligencia_mercado.xlsx
@@ -585,20 +585,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3981-21-LE26</t>
+          <t>771555-9-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN LUMINARIAS RUTA I-512 SECTOR LA CAPILLA COMUNA DE PAREDONES</t>
+          <t>Mejoramiento Cancha de Futbol Fundina Norte RH</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-05T09:12:26.2</t>
+          <t>2026-08-05T10:00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -620,12 +620,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -719,20 +719,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>771555-9-LP26</t>
+          <t>3981-21-LE26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mejoramiento Cancha de Futbol Fundina Norte RH</t>
+          <t>INSTALACIÓN LUMINARIAS RUTA I-512 SECTOR LA CAPILLA COMUNA DE PAREDONES</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:00:00</t>
+          <t>2026-08-05T09:12:26.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -21393,20 +21393,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3981-21-LE26</t>
+          <t>771555-9-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN LUMINARIAS RUTA I-512 SECTOR LA CAPILLA COMUNA DE PAREDONES</t>
+          <t>Mejoramiento Cancha de Futbol Fundina Norte RH</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-05T09:12:26.2</t>
+          <t>2026-08-05T10:00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21428,12 +21428,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -21527,20 +21527,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>771555-9-LP26</t>
+          <t>3981-21-LE26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mejoramiento Cancha de Futbol Fundina Norte RH</t>
+          <t>INSTALACIÓN LUMINARIAS RUTA I-512 SECTOR LA CAPILLA COMUNA DE PAREDONES</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:00:00</t>
+          <t>2026-08-05T09:12:26.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -21562,12 +21562,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
